--- a/data/trans_orig/P24D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2007</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2007 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53872</t>
+          <t>52879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72867</t>
+          <t>73063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>92407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>52525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65591</t>
+          <t>65280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129652</t>
+          <t>130645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153901</t>
+          <t>153350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>51649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79492</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39618</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60225</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97635</t>
+          <t>97566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132167</t>
+          <t>133357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111994</t>
+          <t>110615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139215</t>
+          <t>139837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>57870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79038</t>
+          <t>80184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177976</t>
+          <t>176786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212508</t>
+          <t>212577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>39248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>36742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69508</t>
+          <t>68773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>107537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126243</t>
+          <t>126722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75078</t>
+          <t>74368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171183</t>
+          <t>171918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197163</t>
+          <t>198074</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76198</t>
+          <t>74638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107660</t>
+          <t>106097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106617</t>
+          <t>106294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131009</t>
+          <t>130194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51322</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70497</t>
+          <t>70082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163437</t>
+          <t>165000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194899</t>
+          <t>196459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30916</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>61862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45736</t>
+          <t>47097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63112</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>29013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44364</t>
+          <t>44520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>81993</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104705</t>
+          <t>104312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53737</t>
+          <t>53475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52723</t>
+          <t>52876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79724</t>
+          <t>78525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70615</t>
+          <t>70877</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90704</t>
+          <t>92460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34808</t>
+          <t>34834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109636</t>
+          <t>110835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>136484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70178</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101545</t>
+          <t>98476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81989</t>
+          <t>81722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>132588</t>
+          <t>132982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172470</t>
+          <t>170401</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>133431</t>
+          <t>136500</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>164798</t>
+          <t>164964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78428</t>
+          <t>78695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103566</t>
+          <t>104050</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>222922</t>
+          <t>224991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262804</t>
+          <t>262410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>76339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110863</t>
+          <t>110515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45764</t>
+          <t>45484</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70311</t>
+          <t>71128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>131400</t>
+          <t>129012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172324</t>
+          <t>171782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205161</t>
+          <t>205509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>239685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114906</t>
+          <t>114089</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139453</t>
+          <t>139733</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>328916</t>
+          <t>329458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>369840</t>
+          <t>372228</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>384310</t>
+          <t>387290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>454734</t>
+          <t>456308</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>272592</t>
+          <t>268931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>326520</t>
+          <t>323551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>671967</t>
+          <t>671062</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>767700</t>
+          <t>759321</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>926094</t>
+          <t>924520</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>996518</t>
+          <t>993538</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>527954</t>
+          <t>530923</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>581882</t>
+          <t>585543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1467602</t>
+          <t>1475981</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1563335</t>
+          <t>1564240</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2012</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>81251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102461</t>
+          <t>102538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51872</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71965</t>
+          <t>71611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139096</t>
+          <t>139429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169105</t>
+          <t>169663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,38%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34019</t>
+          <t>33942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>55229</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>46196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95315</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87796</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120273</t>
+          <t>120876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53713</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78378</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151259</t>
+          <t>150207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191726</t>
+          <t>189065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87832</t>
+          <t>87229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120309</t>
+          <t>117538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72840</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>97385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>167597</t>
+          <t>170258</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>208064</t>
+          <t>209116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>60425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55960</t>
+          <t>57306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>82129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113056</t>
+          <t>111677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>66612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87304</t>
+          <t>88345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97711</t>
+          <t>99090</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127691</t>
+          <t>128638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48723</t>
+          <t>48408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72424</t>
+          <t>72042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60785</t>
+          <t>60640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80718</t>
+          <t>79202</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115624</t>
+          <t>113792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145650</t>
+          <t>145044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57311</t>
+          <t>57693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81012</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88069</t>
+          <t>88675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118095</t>
+          <t>119927</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39014</t>
+          <t>39516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58855</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70841</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96831</t>
+          <t>96022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>51883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>22742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>38901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60008</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85998</t>
+          <t>87654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>35732</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53704</t>
+          <t>53990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29650</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45618</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70973</t>
+          <t>70468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96539</t>
+          <t>94972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47822</t>
+          <t>48008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37229</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54080</t>
+          <t>55647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79646</t>
+          <t>80151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92673</t>
+          <t>90837</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125026</t>
+          <t>124251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80988</t>
+          <t>81413</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110788</t>
+          <t>109598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181689</t>
+          <t>179721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225973</t>
+          <t>225776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154215</t>
+          <t>154990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186568</t>
+          <t>188404</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>82483</t>
+          <t>83673</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112283</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246539</t>
+          <t>246736</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>290823</t>
+          <t>292791</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>100309</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134713</t>
+          <t>136270</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>66061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96626</t>
+          <t>96281</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175937</t>
+          <t>175584</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>222143</t>
+          <t>219605</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161441</t>
+          <t>159884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195790</t>
+          <t>195845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110117</t>
+          <t>110462</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140317</t>
+          <t>140682</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280754</t>
+          <t>283292</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>326960</t>
+          <t>327313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>590891</t>
+          <t>588595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>663949</t>
+          <t>664147</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>467390</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>530327</t>
+          <t>527689</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1066822</t>
+          <t>1075336</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1170387</t>
+          <t>1178002</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>687943</t>
+          <t>687745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>761001</t>
+          <t>763297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>438867</t>
+          <t>441505</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>501804</t>
+          <t>505284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1150699</t>
+          <t>1143084</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1254264</t>
+          <t>1245750</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2016</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55694</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>77415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33250</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49922</t>
+          <t>50174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94368</t>
+          <t>93819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121254</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30500</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50637</t>
+          <t>50295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58791</t>
+          <t>58782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85677</t>
+          <t>86226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30676</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>27343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49673</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63849</t>
+          <t>63895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94993</t>
+          <t>95309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155201</t>
+          <t>155133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178365</t>
+          <t>178720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>92108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112283</t>
+          <t>113505</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254897</t>
+          <t>254581</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>286041</t>
+          <t>285995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,74%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25912</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48722</t>
+          <t>49087</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>62896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89050</t>
+          <t>88249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>51505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>50083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88684</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113929</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,61%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75268</t>
+          <t>76842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99109</t>
+          <t>99461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45629</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128102</t>
+          <t>129980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163385</t>
+          <t>161892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40178</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>62445</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42126</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>63378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>86152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119942</t>
+          <t>118064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50448</t>
+          <t>51262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>37164</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>59991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81868</t>
+          <t>83106</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,62%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>33869</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53071</t>
+          <t>52707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34518</t>
+          <t>33993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59906</t>
+          <t>58668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>84173</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32354</t>
+          <t>31777</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51299</t>
+          <t>50122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32489</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78270</t>
+          <t>78607</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36931</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>56453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40569</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56950</t>
+          <t>57430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>82681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107918</t>
+          <t>108188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,08%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56628</t>
+          <t>57163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84566</t>
+          <t>85737</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53257</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80813</t>
+          <t>80443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>119137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157564</t>
+          <t>157448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>110992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>92454</t>
+          <t>92824</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120010</t>
+          <t>118826</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212432</t>
+          <t>212548</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250183</t>
+          <t>250859</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104867</t>
+          <t>103908</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137816</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>98159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126670</t>
+          <t>126905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210333</t>
+          <t>209101</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253430</t>
+          <t>253061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117242</t>
+          <t>118825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150191</t>
+          <t>151150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>87383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116100</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215917</t>
+          <t>216286</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>259014</t>
+          <t>260246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>467578</t>
+          <t>470680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>534850</t>
+          <t>539975</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>379914</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>439527</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>868127</t>
+          <t>868049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>960933</t>
+          <t>964351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>641287</t>
+          <t>636162</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>708559</t>
+          <t>705457</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>482452</t>
+          <t>479802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>544385</t>
+          <t>542065</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1137183</t>
+          <t>1133765</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1229989</t>
+          <t>1230067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2023</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2023 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49012</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39006</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>55931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84159</t>
+          <t>81879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35332</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65216</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94072</t>
+          <t>93444</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65978</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>78474</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112216</t>
+          <t>112390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>61330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89967</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45895</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>64339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114158</t>
+          <t>113984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147417</t>
+          <t>147900</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37967</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39885</t>
+          <t>40285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52194</t>
+          <t>51902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73623</t>
+          <t>73297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>52292</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36722</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64216</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85645</t>
+          <t>85937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17535</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>38067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>44390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70330</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34628</t>
+          <t>35349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56606</t>
+          <t>56860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76450</t>
+          <t>76424</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103429</t>
+          <t>102390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29983</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23054</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54577</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39784</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49175</t>
+          <t>49688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>63183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39486</t>
+          <t>39401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100246</t>
+          <t>99853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69710</t>
+          <t>68112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104802</t>
+          <t>102232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92381</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144336</t>
+          <t>145898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>186464</t>
+          <t>188156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68216</t>
+          <t>70786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>104906</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57689</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80541</t>
+          <t>80022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136624</t>
+          <t>134932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>178752</t>
+          <t>177190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53810</t>
+          <t>54016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36592</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55595</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73671</t>
+          <t>72478</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101594</t>
+          <t>101404</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>130031</t>
+          <t>129825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151676</t>
+          <t>152148</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63565</t>
+          <t>62979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82568</t>
+          <t>81695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>201407</t>
+          <t>201597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>229330</t>
+          <t>230523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,08%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>263266</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325930</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261133</t>
+          <t>259098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>305334</t>
+          <t>304949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>534770</t>
+          <t>533230</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>616261</t>
+          <t>613310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>500846</t>
+          <t>500878</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>565047</t>
+          <t>563542</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>341071</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>385272</t>
+          <t>387307</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>856951</t>
+          <t>859902</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>938442</t>
+          <t>939982</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24D-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>40425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17641</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>29124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>51360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73063</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92407</t>
+          <t>92996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52525</t>
+          <t>51624</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>65362</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130645</t>
+          <t>132164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153350</t>
+          <t>154400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51649</t>
+          <t>52473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80871</t>
+          <t>79023</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>37512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60786</t>
+          <t>59632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97566</t>
+          <t>97213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133357</t>
+          <t>131492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110615</t>
+          <t>112463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>139837</t>
+          <t>139013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57870</t>
+          <t>59024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80184</t>
+          <t>81144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176786</t>
+          <t>178651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212577</t>
+          <t>212930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39248</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36742</t>
+          <t>36174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68773</t>
+          <t>68405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107537</t>
+          <t>108020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126722</t>
+          <t>127033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57164</t>
+          <t>57732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74368</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171918</t>
+          <t>172286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198074</t>
+          <t>197115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63224</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50224</t>
+          <t>50009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74638</t>
+          <t>76469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106097</t>
+          <t>106364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106294</t>
+          <t>106759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130194</t>
+          <t>130564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51355</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70082</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165000</t>
+          <t>164733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196459</t>
+          <t>194628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21469</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>40281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61862</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62860</t>
+          <t>63683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44520</t>
+          <t>44255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81993</t>
+          <t>82073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31892</t>
+          <t>32965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53475</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78525</t>
+          <t>77932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92460</t>
+          <t>91387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110835</t>
+          <t>111428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136484</t>
+          <t>137069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70012</t>
+          <t>67823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98476</t>
+          <t>98460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>57093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81722</t>
+          <t>83527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>132982</t>
+          <t>131801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>170401</t>
+          <t>171253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>136500</t>
+          <t>136516</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>164964</t>
+          <t>167153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78695</t>
+          <t>76890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104050</t>
+          <t>103324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224991</t>
+          <t>224139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262410</t>
+          <t>263591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>76742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>110515</t>
+          <t>108335</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>46494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71128</t>
+          <t>71871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>129012</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>171782</t>
+          <t>169425</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>205509</t>
+          <t>207689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>239685</t>
+          <t>239282</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139733</t>
+          <t>138723</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>329458</t>
+          <t>331815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372228</t>
+          <t>371504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>387290</t>
+          <t>387022</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>456308</t>
+          <t>457836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>323551</t>
+          <t>324646</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>671062</t>
+          <t>673899</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>759321</t>
+          <t>762196</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>924520</t>
+          <t>922992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>993538</t>
+          <t>993806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>530923</t>
+          <t>529828</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>585543</t>
+          <t>586178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1475981</t>
+          <t>1473106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1564240</t>
+          <t>1561403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>80378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102538</t>
+          <t>102418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51735</t>
+          <t>52138</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>72494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139429</t>
+          <t>139283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169663</t>
+          <t>170374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55229</t>
+          <t>56102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26320</t>
+          <t>25437</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46196</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>64037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94982</t>
+          <t>95128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>88231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120876</t>
+          <t>119474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>53268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>78630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150207</t>
+          <t>151121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189065</t>
+          <t>191848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87229</t>
+          <t>88631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>117538</t>
+          <t>119874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72906</t>
+          <t>72588</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97385</t>
+          <t>97950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170258</t>
+          <t>167475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>208202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60425</t>
+          <t>61112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38477</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111677</t>
+          <t>111875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66612</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88345</t>
+          <t>88262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>27418</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>99090</t>
+          <t>98892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128638</t>
+          <t>127513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>49006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72042</t>
+          <t>72218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>60700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79202</t>
+          <t>80839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113792</t>
+          <t>115803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145044</t>
+          <t>146589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81327</t>
+          <t>80729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43344</t>
+          <t>43284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88675</t>
+          <t>87130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119927</t>
+          <t>117916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69185</t>
+          <t>71564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96022</t>
+          <t>96891</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>59948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87654</t>
+          <t>85275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53990</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>29782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>46114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70468</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94972</t>
+          <t>95883</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,66%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>29581</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48008</t>
+          <t>47811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37331</t>
+          <t>37097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55647</t>
+          <t>54736</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80151</t>
+          <t>79433</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90837</t>
+          <t>90639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124251</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81413</t>
+          <t>81827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109598</t>
+          <t>110679</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179721</t>
+          <t>180863</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>225776</t>
+          <t>222248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154990</t>
+          <t>155547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>188404</t>
+          <t>188602</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>83673</t>
+          <t>82592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111858</t>
+          <t>111444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>246736</t>
+          <t>250264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292791</t>
+          <t>291649</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100309</t>
+          <t>99914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136270</t>
+          <t>134775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66061</t>
+          <t>66064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96281</t>
+          <t>95430</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175584</t>
+          <t>177289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219605</t>
+          <t>223648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159884</t>
+          <t>161379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195845</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110462</t>
+          <t>111313</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>140682</t>
+          <t>140679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283292</t>
+          <t>279249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327313</t>
+          <t>325608</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>588595</t>
+          <t>587726</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>662984</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>461690</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>527689</t>
+          <t>528034</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1075336</t>
+          <t>1067264</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1178002</t>
+          <t>1169235</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>687745</t>
+          <t>688908</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>763297</t>
+          <t>764166</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>441505</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>505284</t>
+          <t>507504</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1143084</t>
+          <t>1151851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1245750</t>
+          <t>1253822</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56036</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77415</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50174</t>
+          <t>50120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93819</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121263</t>
+          <t>121453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50295</t>
+          <t>51302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58782</t>
+          <t>58592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86226</t>
+          <t>85863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53908</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27343</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>63618</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>96149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155133</t>
+          <t>155248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178720</t>
+          <t>178580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92108</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113505</t>
+          <t>114175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254581</t>
+          <t>253741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>285995</t>
+          <t>286272</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44826</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31320</t>
+          <t>31593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49087</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62896</t>
+          <t>61791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88249</t>
+          <t>88168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,61%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70036</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50083</t>
+          <t>49810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89485</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>115943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76842</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99461</t>
+          <t>100558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67875</t>
+          <t>67727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129980</t>
+          <t>127150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161892</t>
+          <t>159932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39826</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40882</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63378</t>
+          <t>62947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86152</t>
+          <t>88112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118064</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32424</t>
+          <t>32685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51262</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37164</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59991</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83106</t>
+          <t>84335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33869</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52707</t>
+          <t>52446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33993</t>
+          <t>34109</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>58668</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81783</t>
+          <t>81967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31777</t>
+          <t>31948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50122</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32816</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>51935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78607</t>
+          <t>76433</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>36924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>56282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57430</t>
+          <t>56889</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82681</t>
+          <t>84855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108188</t>
+          <t>109353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57163</t>
+          <t>57378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>85778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54441</t>
+          <t>53772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80443</t>
+          <t>80414</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119137</t>
+          <t>120295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157448</t>
+          <t>158211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110992</t>
+          <t>110951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139566</t>
+          <t>139351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>92824</t>
+          <t>92853</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>118826</t>
+          <t>119495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212548</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>250859</t>
+          <t>249701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103908</t>
+          <t>102606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136233</t>
+          <t>134775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98159</t>
+          <t>98693</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126905</t>
+          <t>127732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209101</t>
+          <t>209390</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>253061</t>
+          <t>255032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118825</t>
+          <t>120283</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151150</t>
+          <t>152452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87383</t>
+          <t>86556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>116129</t>
+          <t>115595</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>216286</t>
+          <t>214315</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>260246</t>
+          <t>259957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>470680</t>
+          <t>470649</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>539975</t>
+          <t>540294</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>379914</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>442177</t>
+          <t>441009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>868049</t>
+          <t>870043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>964351</t>
+          <t>961813</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>636162</t>
+          <t>635843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>705457</t>
+          <t>705488</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>479802</t>
+          <t>480970</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>542065</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1133765</t>
+          <t>1136303</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1230067</t>
+          <t>1228073</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37592</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26507</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49119</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>26184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38865</t>
+          <t>38356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55931</t>
+          <t>55606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81879</t>
+          <t>78017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46752</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26166</t>
+          <t>27977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39752</t>
+          <t>40149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>75654</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93444</t>
+          <t>86678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>51408</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>66279</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42875</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>35120</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51675</t>
+          <t>52510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>94829</t>
+          <t>95153</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78474</t>
+          <t>78151</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112390</t>
+          <t>113162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76470</t>
+          <t>80692</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61330</t>
+          <t>65821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>93739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55076</t>
+          <t>57726</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46276</t>
+          <t>48961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64339</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>131545</t>
+          <t>138418</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113984</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147900</t>
+          <t>155420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>128423</t>
+          <t>132100</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128423</t>
+          <t>132100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128423</t>
+          <t>132100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97951</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97951</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97951</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>226374</t>
+          <t>233571</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>226374</t>
+          <t>233571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>226374</t>
+          <t>233571</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29515</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40285</t>
+          <t>40318</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62839</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51902</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>47962</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35435</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52292</t>
+          <t>56412</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>78245</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>67372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85937</t>
+          <t>88381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>64022</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>137839</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>137839</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137839</t>
+          <t>143583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>48125</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,17 +11761,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56401</t>
+          <t>66370</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44390</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70356</t>
+          <t>83183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>49,22%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47008</t>
+          <t>55359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>41694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>68027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,17 +11874,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>37615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>56043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>90379</t>
+          <t>102642</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76424</t>
+          <t>85829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>118091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74141</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74141</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74141</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72638</t>
+          <t>79193</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72638</t>
+          <t>79193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72638</t>
+          <t>79193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>146780</t>
+          <t>169012</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29780</t>
+          <t>36279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>25083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>67763</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>63547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61152</t>
+          <t>70508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,17 +12482,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30941</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23281</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>40217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>57377</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49688</t>
+          <t>49698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63183</t>
+          <t>63827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29774</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>40443</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,17 +12595,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>92193</t>
+          <t>93488</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83317</t>
+          <t>84644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99853</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>98090</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68112</t>
+          <t>82901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102232</t>
+          <t>113708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>97516</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70048</t>
+          <t>84718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92220</t>
+          <t>109438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>165765</t>
+          <t>195607</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>145898</t>
+          <t>175625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188156</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,61%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>88813</t>
+          <t>92105</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>76487</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104906</t>
+          <t>107294</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68510</t>
+          <t>76045</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>64123</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>157323</t>
+          <t>168149</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>134932</t>
+          <t>146913</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>177190</t>
+          <t>188131</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>173018</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>173018</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>173018</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150070</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>323088</t>
+          <t>363756</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>323088</t>
+          <t>363756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>323088</t>
+          <t>363756</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>49202</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>61639</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>45571</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>62234</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>87245</t>
+          <t>100863</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72478</t>
+          <t>85466</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101404</t>
+          <t>118623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>142168</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129825</t>
+          <t>147999</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152148</t>
+          <t>172682</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>73589</t>
+          <t>83648</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81695</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>215756</t>
+          <t>244083</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>201597</t>
+          <t>226323</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>230523</t>
+          <t>259480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>303001</t>
+          <t>344946</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>303001</t>
+          <t>344946</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>303001</t>
+          <t>344946</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>263266</t>
+          <t>285482</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>325930</t>
+          <t>353950</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>259098</t>
+          <t>282477</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>304949</t>
+          <t>329045</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>533230</t>
+          <t>588102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>613310</t>
+          <t>669762</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>535514</t>
+          <t>574529</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>500878</t>
+          <t>540410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>563542</t>
+          <t>608878</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>364696</t>
+          <t>393914</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>387307</t>
+          <t>418468</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>900209</t>
+          <t>968443</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>859902</t>
+          <t>925544</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>939982</t>
+          <t>1007204</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
